--- a/FAST_Report.xlsx
+++ b/FAST_Report.xlsx
@@ -8,40 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HARI\ciATHENA_Backup\ciathena_autoamtion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FAFF489-E50F-42A2-A907-A57EF75E4473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F82C5D1-0F40-4B43-8FC5-9648A3AA499C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$S$16</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="96">
   <si>
     <t>Question</t>
   </si>
   <si>
-    <t>Answer</t>
+    <t>answer</t>
   </si>
   <si>
     <t>SQL_Query</t>
@@ -71,19 +55,22 @@
     <t>chat_match</t>
   </si>
   <si>
-    <t>Share_icon</t>
-  </si>
-  <si>
-    <t>Save_icon</t>
-  </si>
-  <si>
-    <t>View_fullscreen_icon</t>
+    <t>raw_sql_comparision_result</t>
+  </si>
+  <si>
+    <t>share_icon</t>
+  </si>
+  <si>
+    <t>save_icon</t>
+  </si>
+  <si>
+    <t>view_fullscreen_icon</t>
   </si>
   <si>
     <t>data_view_icon</t>
   </si>
   <si>
-    <t>Download_icon</t>
+    <t>download_icon</t>
   </si>
   <si>
     <t>STATUS</t>
@@ -92,7 +79,7 @@
     <t>Give me the total market volume by Cardizor access.</t>
   </si>
   <si>
-    <t>The total market volume varies significantly by access favorability. For "01 - Unrestricted" access, the market volume is 191,212.57, with Cardizor contributing 40,031.26, representing a 20.94% market share. In "02 - Restricted SSE," the market volume is 61,164.56, with Cardizor accounting for 9,347.02, achieving a 15.28% share. For "03 - Restricted DSE," the market volume is 83,716.94, with Cardizor at 6,082.58, holding a 7.27% share. Other categories, such as "04 - Restricted TSE" and "05 - Restricted QSE," show lower market volumes of 27,574.55 and 12,334.25, with Cardizor's shares at 6.84% and 8.83%, respectively. In "98 - Not Covered," the market volume is 136,006.59, with Cardizor contributing 11,036.11, representing an 8.11% share.</t>
+    <t>The  total  market  volume  by  Cardizor  access  shows  that  'Unrestricted'  access  leads  with  191,212.57,  followed  by  'Restricted  DSE'  at  83,716.94  and  'Not  Covered'  at  136,006.59.  'Restricted  SSE'  contributes  61,164.56,  while  'Restricted  TSE'  and  'Restricted</t>
   </si>
   <si>
     <t>SELECT
@@ -124,24 +111,24 @@
     <t>combo_bar_line</t>
   </si>
   <si>
-    <t>PASS</t>
+    <t>FAIL</t>
   </si>
   <si>
     <t>How does Cardizor’s access favorability compare to key competitors?</t>
   </si>
   <si>
-    <t>Cardizor has 37.35% of its market volume under "Unrestricted" access, which is lower than Competitor 1 at 44.35%, Competitor 2 at 99.50%, and Competitor 3 at 90.93%. Cardizor also has a higher proportion of its market volume in restricted and "Not Covered" categories compared to these competitors, with 26.56% "Not Covered" versus 22.82% for Competitor 1, 0.18% for Competitor 2, and 8.50% for Competitor 3. This indicates that Cardizor faces more access restrictions relative to its key competitors.</t>
-  </si>
-  <si>
-    <t>WITH ProductAccessVolume AS ( SELECT
+    <t>Cardizor's  access  favorability  is  concentrated  in  the  'Unrestricted'  tier  at  37.35%,  which  is  lower  than  Competitor  1  (44.35%),  Competitor  2  (99.50%),  and  Competitor  3  (90.93%).  Cardizor  also  has  a  higher  proportion  of  market  volume  in  restricted  tiers,  such  as  'Restricted  SSE'  (11.95%)  and  'Restricted  DSE'  (16.35%),  compared  to  Competitor  2  and</t>
+  </si>
+  <si>
+    <t>WITH agg AS ( SELECT
   "PRODUCT",
   "ACCESS",
   SUM("MARKET_VOLUME") AS "TotalMarketVolume"
 FROM "fast"."Updated_FAST_Table_MVP_Unpivot"
-WHERE "METRIC" = 'TRX' AND "PRODUCT" IN ('CARDIZOR', 'COMPETITOR1', 'COMPETITOR2', 'COMPETITOR3')
-GROUP BY "PRODUCT", "ACCESS" ) SELECT pav."PRODUCT", pav."ACCESS", pav."TotalMarketVolume" * 100.0 / NULLIF(SUM(pav."TotalMarketVolume") OVER(PARTITION BY pav."PRODUCT"), 0) AS "Market Volume Percentage"
-FROM ProductAccessVolume AS pav
-ORDER BY pav."PRODUCT", pav."ACCESS";</t>
+WHERE "METRIC"='TRX' AND "PRODUCT" IN ('CARDIZOR','COMPETITOR1','COMPETITOR2','COMPETITOR3')
+GROUP BY "PRODUCT","ACCESS" ) SELECT t."PRODUCT", t."ACCESS", t."TotalMarketVolume" * 100.0 / NULLIF(SUM(t."TotalMarketVolume") OVER(PARTITION BY t."PRODUCT"),0) AS "% Market Volume"
+FROM agg t
+ORDER BY t."PRODUCT",t."ACCESS";</t>
   </si>
   <si>
     <t>SELECT
@@ -173,17 +160,17 @@
     <t>How is the Payer Mix of Cardizor different from Payer-Mix of Competitor1?</t>
   </si>
   <si>
-    <t>Cardizor's payer mix shows a stronger reliance on Medicare, with 21.38% of TRx coming from this channel, compared to Competitor1's 8.14%. Conversely, Competitor1 has a higher proportion of TRx from Commercial payers at 91.86%, while Cardizor's Commercial share is lower at 78.62%. This indicates that Cardizor has a more balanced distribution between Commercial and Medicare channels, whereas Competitor1 is heavily skewed toward Commercial payers.</t>
+    <t>Cardizor  relies  more  heavily  on  Medicare,  with  21.38%  of  its  payer  mix  coming  from</t>
   </si>
   <si>
     <t>SELECT
   "PRODUCT",
   "PAYMENT_CHANNEL",
-  ROUND( SUM("VOLUME") * 100.0 / NULLIF(SUM(SUM("VOLUME")) OVER (PARTITION BY "PRODUCT"),0), 2 ) AS "Payer Mix"
-FROM "fast"."Updated_FAST_Table_MVP_Unpivot"
-WHERE "METRIC"='TRX' AND UPPER("PRODUCT") IN ('CARDIZOR','COMPETITOR1')
-GROUP BY "PRODUCT","PAYMENT_CHANNEL"
-ORDER BY "PRODUCT","PAYMENT_CHANNEL";</t>
+  ROUND( SUM("VOLUME") * 100.0 / NULLIF(SUM(SUM("VOLUME")) OVER (PARTITION BY "PRODUCT"), 0), 2 ) AS "Payer Mix"
+FROM "fast"."Updated_FAST_Table_MVP_Unpivot"
+WHERE "METRIC" = 'TRX' AND UPPER("PRODUCT") IN ('CARDIZOR', 'COMPETITOR1')
+GROUP BY "PRODUCT", "PAYMENT_CHANNEL"
+ORDER BY "PRODUCT", "PAYMENT_CHANNEL";</t>
   </si>
   <si>
     <t>SELECT
@@ -206,7 +193,7 @@
     <t>Show me distribution of cardizor market share between favorable and unfavorable access segments</t>
   </si>
   <si>
-    <t>Cardizor's market share is distributed with 71.08% in the Favorable Access segment and 28.92% in the Unfavorable Access segment. This indicates a strong presence in areas with favorable access conditions.</t>
+    <t>Cardizor's  market  share  is  significantly  stronger  in  the  Favorable  Access  segment,  where  it  accounts  for  71.08%  of  the  market.  In  contrast,  its  share  in  the  Unfavorable</t>
   </si>
   <si>
     <t>WITH Vols AS ( SELECT
@@ -250,10 +237,13 @@
     <t>pie</t>
   </si>
   <si>
+    <t>PASS</t>
+  </si>
+  <si>
     <t>Give me unique count of HCPs on primary axis and corresponding market share on Secondary axis by FAST Score category</t>
   </si>
   <si>
-    <t>The unique count of HCPs prescribing CARDIZOR increases steadily from 74 in the 0-10% FAST Score category to a peak of 2,245 in the 40-50% category, before declining in higher FAST Score ranges. Correspondingly, the market share starts at 6.43% in the 0-10% category and rises significantly, peaking at 31.26% in the 70-80% category. This indicates a strong correlation between higher FAST Scores and increased market share, despite a decline in HCP count in the upper ranges.</t>
+    <t>The  unique  count  of  HCPs  increases  across  the  FAST  Score  categories,  peaking  at  2,245</t>
   </si>
   <si>
     <t>SELECT
@@ -275,7 +265,21 @@
     <t>Who are the largest payers for Cardizor and competitors?</t>
   </si>
   <si>
-    <t>The largest payers for Cardizor and its competitors, based on total transaction (TRx) volume, are OptumRx Administered Plans, CVS Health Administered Plans, and UnitedHealthcare. OptumRx leads with a total TRx volume of 38,919.99, followed by CVS Health at 36,399.99 and UnitedHealthcare at 34,681.99. These three dominate the market, with significant contributions across all products, including Cardizor and its competitors.</t>
+    <t>UnitedHealthcare  is  the  largest  payer  for  Cardizor,  with  a  volume  of  6,542.99  TRx,  followed  by  CVS  Health  Administered  Plans  at  2,989.99  TRx  and  OptumRx  Administered  Plans  at  2,888.99  TRx.  Across</t>
+  </si>
+  <si>
+    <t>WITH LatestData AS ( SELECT
+  "PAYER_NAME",
+  "PRODUCT",
+  SUM("VOLUME") AS "VOLUME"
+FROM "fast"."Updated_FAST_Table_MVP_Unpivot"
+WHERE "METRIC" = 'TRX'
+GROUP BY "PAYER_NAME","PRODUCT" ), PayerAggregates AS ( SELECT "PAYER_NAME", SUM(CASE WHEN "PRODUCT" = 'CARDIZOR' THEN "VOLUME" ELSE 0 END) AS "Cardizor Volume", SUM(CASE WHEN "PRODUCT" = 'COMPETITOR1' THEN "VOLUME" ELSE 0 END) AS "Competitor 1 Volume", SUM(CASE WHEN "PRODUCT" = 'COMPETITOR2' THEN "VOLUME" ELSE 0 END) AS "Competitor 2 Volume", SUM(CASE WHEN "PRODUCT" = 'COMPETITOR3' THEN "VOLUME" ELSE 0 END) AS "Competitor 3 Volume", SUM("VOLUME") AS "Total Market Volume"
+FROM LatestData
+GROUP BY "PAYER_NAME" ) SELECT *
+FROM PayerAggregates
+ORDER BY "Total Market Volume" DESC
+LIMIT 10;</t>
   </si>
   <si>
     <t>WITH LatestData AS ( SELECT
@@ -301,7 +305,7 @@
     <t>Which payers show high or low differentiation of access across products?</t>
   </si>
   <si>
-    <t>All payers in the dataset exhibit "Moderate Differentiation" in access across products, with varying levels of market volume. For example, OptumRx Administered Plans and UnitedHealthcare show significant market volumes of 38,920 and 34,682, respectively, while maintaining moderate differentiation in access favorability. Similarly, smaller payers like UnitedHealthcare (TX) and Ambetter from Sunshine Health Plan (FL) also demonstrate moderate differentiation but with lower market volumes of 751 and 751, respectively. This indicates a consistent trend of moderate differentiation across payers, regardless of their market size.</t>
+    <t>All  payers  analyzed,  including  OptumRx,  UnitedHealthcare,  Express  Scripts,  and  others,  exhibit  "Moderate  Differentiation"  in  access  across  products.  While  access  favorability  varies,  most  plans  show</t>
   </si>
   <si>
     <t>WITH LatestPeriodData AS ( SELECT
@@ -321,7 +325,7 @@
 FROM LatestPeriodData ), AllTimeMarket AS ( SELECT "PAYER_NAME", SUM("VOLUME") AS "TotalMarketVolume_AllTime"
 FROM "fast"."Updated_FAST_Table_MVP_Unpivot"
 WHERE "METRIC" = 'TRX'
-GROUP BY "PAYER_NAME" ) SELECT pa."PAYER_NAME", pa."CARDIZOR_ACCESS_FAVORABILITY", pa."COMPETITOR1_ACCESS_FAVORABILITY", pa."COMPETITOR2_ACCESS_FAVORABILITY", pa."COMPETITOR3_ACCESS_FAVORABILITY", m."TotalMarketVolume_AllTime" AS "Total Market Volume", CASE WHEN ( ( ABS(pa."CARDIZOR_ACCESS_FAVORABILITY_CODE" - pa."COMPETITOR1_ACCESS_FAVORABILITY_CODE") + ABS(pa."CARDIZOR_ACCESS_FAVORABILITY_CODE" - pa."COMPETITOR2_ACCESS_FAVORABILITY_CODE") + ABS(pa."CARDIZOR_ACCESS_FAVORABILITY_CODE" - pa."COMPETITOR3_ACCESS_FAVORABILITY_CODE") )::numeric / 3.0 ) IN (0,1) THEN 'Low Differentiation' WHEN ( ( ABS(pa."CARDIZOR_ACCESS_FAVORABILITY_CODE" - pa."COMPETITOR1_ACCESS_FAVORABILITY_CODE") + ABS(pa."CARDIZOR_ACCESS_FAVORABILITY_CODE" - pa."COMPETITOR2_ACCESS_FAVORABILITY_CODE") + ABS(pa."CARDIZOR_ACCESS_FAVORABILITY_CODE" - pa."COMPETITOR3_ACCESS_FAVORABILITY_CODE") )::numeric / 3.0 ) = 5 THEN 'High Differentiation' ELSE 'Moderate Differentiation' END AS "AccessDifferentiationLevel"
+GROUP BY "PAYER_NAME" ) SELECT pa."PAYER_NAME", pa."CARDIZOR_ACCESS_FAVORABILITY", pa."COMPETITOR1_ACCESS_FAVORABILITY", pa."COMPETITOR2_ACCESS_FAVORABILITY", pa."COMPETITOR3_ACCESS_FAVORABILITY", m."TotalMarketVolume_AllTime" AS "Total Market Volume", CASE WHEN ( ( ABS(pa."CARDIZOR_ACCESS_FAVORABILITY_CODE" - pa."COMPETITOR1_ACCESS_FAVORABILITY_CODE") + ABS(pa."CARDIZOR_ACCESS_FAVORABILITY_CODE" - pa."COMPETITOR2_ACCESS_FAVORABILITY_CODE") + ABS(pa."CARDIZOR_ACCESS_FAVORABILITY_CODE" - pa."COMPETITOR3_ACCESS_FAVORABILITY_CODE") )::numeric / 3 ) IN (0,1) THEN 'Low Differentiation' WHEN ( ( ABS(pa."CARDIZOR_ACCESS_FAVORABILITY_CODE" - pa."COMPETITOR1_ACCESS_FAVORABILITY_CODE") + ABS(pa."CARDIZOR_ACCESS_FAVORABILITY_CODE" - pa."COMPETITOR2_ACCESS_FAVORABILITY_CODE") + ABS(pa."CARDIZOR_ACCESS_FAVORABILITY_CODE" - pa."COMPETITOR3_ACCESS_FAVORABILITY_CODE") )::numeric / 3 ) = 5 THEN 'High Differentiation' ELSE 'Moderate Differentiation' END AS "AccessDifferentiationLevel"
 FROM PayerAccessAggregated pa
 LEFT
 JOIN AllTimeMarket m
@@ -355,16 +359,13 @@
 ORDER BY "AccessDifferentiationLevel" DESC, m."TotalMarketVolume_AllTime" DESC;</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>FAIL</t>
+    <t>Sankey Chart</t>
   </si>
   <si>
     <t>How much suppression is Cardizor experiencing in performance due to restrictive access?</t>
   </si>
   <si>
-    <t>Cardizor is experiencing significant suppression in performance due to restrictive access. In the Commercial channel, only 11.96 TRx out of a potential 17.49 TRx are achieved, reflecting a notable gap. Similarly, in the Medicare channel, 26.92 TRx are realized compared to a potential 31.78 TRx, further highlighting the impact of restricted access on its market performance.</t>
+    <t>Cardizor's  performance  is  significantly  impacted  by  restrictive  access,  with  the  'Commercial'  payment  channel  experiencing  a  suppression  ratio  of  31.66%,  despite  having  a  favorable  access  share  of  17.49%  and  a  market  share</t>
   </si>
   <si>
     <t>WITH agg AS ( SELECT
@@ -386,7 +387,7 @@
     <t>How is market share trending against FAST access score groups among Cardizor writers?</t>
   </si>
   <si>
-    <t>Market share among Cardizor writers increases consistently as FAST access scores rise. It starts at 6.43% in the 0-10% FAST score group and peaks at 31.26% in the 70-80% group. This trend indicates a strong positive correlation between higher FAST access scores and greater market share among these HCPs.</t>
+    <t>Cardizor's  market  share  shows  a  clear  upward  trend  as  FAST  access  scores  increase.  It  starts  at  6.43%  in  the  0-10%  score  group  and  peaks  at  31.26%  in  the</t>
   </si>
   <si>
     <t>SELECT
@@ -412,7 +413,7 @@
     <t>What is the distribution of Cardizor HCPs by FAST Access Score categories?</t>
   </si>
   <si>
-    <t>Cardizor HCPs are distributed across FAST Access Score categories with the highest concentration in the 40-50% range, accounting for 21.09% of HCPs (2,245 individuals). This is followed by the 30-40% range at 19.81% (2,109 HCPs) and the 50-60% range at 16.44% (1,750 HCPs). Lower ranges, such as 0-10% and 10-20%, have significantly fewer HCPs, representing 0.70% (74 HCPs) and 5.31% (565 HCPs), respectively.</t>
+    <t>The  distribution  of  Cardizor  HCPs  by  FAST  Access  Score  categories  shows  that  the  majority  fall  within  the  30-50%  range,  with  19.81%  in  the  30-40%  category  and  21.09%  in  the  40-50%  category.  Lower  categories,  such  as  0-10%  and  10-20%,  account  for  only  0.69%  and  5.31%</t>
   </si>
   <si>
     <t>SELECT
@@ -428,7 +429,7 @@
     <t>Which HCP cohorts present incremental opportunity potential in the Market or the Brand, and Access Favorability?</t>
   </si>
   <si>
-    <t>HCP cohorts with "HIGH" market and brand access scores, particularly in BUCKET 3 and BUCKET 2, present the most significant incremental opportunity potential, with incremental TRx opportunities of 13,530 and 10,225, respectively. These cohorts also show strong market capture percentages of 40.04% and 31.40%. Additionally, "MEDIUM" access cohorts in BUCKET 3 and BUCKET 5 demonstrate notable potential, with incremental TRx opportunities of 9,572 and 8,072, and market capture percentages exceeding 40%. Cohorts with "LOW" access scores generally show lower incremental opportunities and market capture percentages, indicating less favorable potential.</t>
+    <t>High-potential  HCP  cohorts  with  favorable  access  scores  are  concentrated  in  the  "HIGH"  market  and  brand  volume  segments,  particularly  in  BUCKET  3,  BUCKET  2,  and  BUCKET  5.  These  cohorts  demonstrate  significant  incremental  TRx  opportunities,  with  BUCKET  3  showing  the  highest</t>
   </si>
   <si>
     <t>WITH volume_totals AS ( SELECT
@@ -453,7 +454,7 @@
     <t>Which HCPs are advantaged in FAST Score but underperforming in prescribing?</t>
   </si>
   <si>
-    <t>HCPs such as "31927082" and "55357702" demonstrate high FAST Access Scores of 0.0868 and 0.0826, respectively, but their prescribing performance for Cardizor is notably low, with market share percentages of 4.38% and 0.0%. Similarly, HCPs like "19700631" and "19703376" also have strong FAST Access Scores of 0.0790 and 0.0750 but show no prescribing activity for Cardizor. These HCPs represent opportunities where high access potential is not translating into prescribing behavior.</t>
+    <t>Several  HCPs  demonstrate  high  FAST  Scores,  indicating  strong  potential  for  access,  but  are  underperforming  in  prescribing.  For  example,  HCPs  like  "55357702,"  "19700631,"  and  "19703376"  have  FAST</t>
   </si>
   <si>
     <t>WITH HCPPerformance AS ( SELECT
@@ -484,24 +485,26 @@
 LIMIT 10;</t>
   </si>
   <si>
+    <t>Bubble Chart</t>
+  </si>
+  <si>
     <t>scatter</t>
   </si>
   <si>
     <t>Which HCPs are disadvantaged in FAST Score but still high prescribers?</t>
   </si>
   <si>
-    <t>HCPs with a FAST Access Score of 0.0 but still demonstrating high prescribing volumes for Cardizor include HCP 36505827, who leads with a TRx volume of 38.76, followed by HCP 55040631 with 22.99, and HCP 28889698 with 17.88. Other notable prescribers in this category include HCP 5055833 at 13.77 and HCP 30783496 at 13. These HCPs represent a significant prescribing impact despite their disadvantaged FAST Access Scores.</t>
-  </si>
-  <si>
-    <t>WITH HCPPerformance AS ( SELECT
+    <t>Several  HCPs  with  a  FAST  Access  Score  of  0.0  are  still  high  prescribers  of  Cardizor,  indicating  a  potential  gap  in  access  or  support.  Notable  examples  include  HCP  36505827  with  a  prescribing  volume  of  38.76  TRx,  HCP  55040631  with  23  TRx,  and  HCP  28889698  with  17.88  TRx.  These  individuals  demonstrate</t>
+  </si>
+  <si>
+    <t>SELECT
   "HCP_ID",
   "HCP_FAST_ACCESS_SCORE",
   SUM("VOLUME") AS "TotalCardizorVolume"
 FROM "fast"."Updated_FAST_Table_MVP_Unpivot"
 WHERE "METRIC" = 'TRX' AND UPPER("PRODUCT") = 'CARDIZOR' AND "VOLUME" &gt; 0
-GROUP BY "HCP_ID", "HCP_FAST_ACCESS_SCORE" ) SELECT h."HCP_ID", h."HCP_FAST_ACCESS_SCORE", h."TotalCardizorVolume"
-FROM HCPPerformance h
-ORDER BY h."HCP_FAST_ACCESS_SCORE" ASC, h."TotalCardizorVolume" DESC
+GROUP BY "HCP_ID", "HCP_FAST_ACCESS_SCORE"
+ORDER BY "HCP_FAST_ACCESS_SCORE" ASC, "TotalCardizorVolume" DESC
 LIMIT 10;</t>
   </si>
   <si>
@@ -522,7 +525,7 @@
     <t xml:space="preserve">Give me US state wise distribution of Cardizor Trx? </t>
   </si>
   <si>
-    <t>Cardizor TRx volumes are highest in Texas, reaching 7,821.85, followed by New York with 5,114.84 and California at 3,662.05. Florida and Illinois also show significant activity with 3,538.98 and 3,336.31 TRx, respectively. States like New Mexico (63.97) and Alaska (113.71) report the lowest TRx volumes, while "Unknown" entries account for 114.</t>
+    <t>Cardizor  TRx  volumes  are  highest  in  Texas,  reaching  7821.85,  followed  by  strong  performances  in  New  York  (5114.84)  and  California  (3662.05).  Florida  (3538.98)  and  Illinois  (3336.31)  also  show  significant  activity,  while  Ohio,  North</t>
   </si>
   <si>
     <t>SELECT
@@ -531,7 +534,8 @@
 FROM "fast"."Updated_FAST_Table_MVP_Unpivot"
 WHERE "METRIC" = 'TRX' AND "PRODUCT" = 'CARDIZOR'
 GROUP BY "STATE"
-ORDER BY "CardizorTRXVolume" DESC;</t>
+ORDER BY "CardizorTRXVolume" DESC
+LIMIT 10;</t>
   </si>
   <si>
     <t>US Heatmap Chart</t>
@@ -642,41 +646,29 @@
 ORDER BY scaled_fast_access_score DESC;</t>
   </si>
   <si>
-    <t>none</t>
+    <t>None</t>
   </si>
   <si>
     <t>benchmark_cluster</t>
   </si>
   <si>
-    <t>Manully run</t>
-  </si>
-  <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>correct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wrong </t>
-  </si>
-  <si>
-    <t>showing chart</t>
-  </si>
-  <si>
-    <t>chart not loading</t>
-  </si>
-  <si>
-    <t>chart loaded - PASS</t>
-  </si>
-  <si>
-    <t>no chart icons</t>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>not same result</t>
+  </si>
+  <si>
+    <t>No response generated</t>
+  </si>
+  <si>
+    <t>no raw sql found from input BE response</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -684,20 +676,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -712,15 +703,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1023,23 +1008,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.88671875" customWidth="1"/>
-    <col min="2" max="2" width="20.109375" customWidth="1"/>
-    <col min="3" max="3" width="22.5546875" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" customWidth="1"/>
-    <col min="5" max="5" width="24.88671875" customWidth="1"/>
-    <col min="6" max="6" width="8.5546875" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="9.5546875" customWidth="1"/>
-    <col min="11" max="11" width="13.109375" customWidth="1"/>
-    <col min="17" max="17" width="8.5546875" customWidth="1"/>
-    <col min="18" max="18" width="14" customWidth="1"/>
-    <col min="19" max="19" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" customWidth="1"/>
+    <col min="9" max="9" width="11.109375" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" customWidth="1"/>
+    <col min="11" max="11" width="7.21875" customWidth="1"/>
+    <col min="12" max="12" width="13.44140625" customWidth="1"/>
+    <col min="19" max="19" width="26.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -1094,22 +1075,28 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -1121,10 +1108,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
@@ -1144,94 +1131,100 @@
       <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q2" t="s">
-        <v>23</v>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0.46733668341708551</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="s">
         <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0.2407407407407407</v>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" t="b">
-        <v>1</v>
-      </c>
-      <c r="N3" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0.89341692789968652</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" t="s">
-        <v>29</v>
-      </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
@@ -1250,25 +1243,28 @@
       <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q4" t="s">
-        <v>23</v>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -1280,10 +1276,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -1303,25 +1299,28 @@
       <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q5" t="s">
-        <v>23</v>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -1333,13 +1332,13 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="b">
         <v>1</v>
@@ -1356,40 +1355,43 @@
       <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q6" t="s">
-        <v>23</v>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0.91738268341044282</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -1409,84 +1411,87 @@
       <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q7" t="s">
-        <v>23</v>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="3" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="2" t="s">
+    <row r="8" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.97940048302315674</v>
+      </c>
+      <c r="H8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0.97884424251029389</v>
-      </c>
-      <c r="H8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>96</v>
+      <c r="K8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -1498,10 +1503,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
@@ -1521,78 +1526,87 @@
       <c r="P9" t="b">
         <v>1</v>
       </c>
-      <c r="Q9" t="s">
-        <v>23</v>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" t="s">
+    <row r="10" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="B10" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10">
+      <c r="C10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
         <v>0.95023696682464454</v>
       </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>43</v>
-      </c>
-      <c r="J10" t="s">
-        <v>44</v>
-      </c>
-      <c r="K10" t="b">
-        <v>1</v>
-      </c>
-      <c r="L10" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" t="b">
-        <v>1</v>
-      </c>
-      <c r="N10" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" t="b">
-        <v>1</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>23</v>
+      <c r="H10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -1604,13 +1618,13 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -1627,324 +1641,300 @@
       <c r="P11" t="b">
         <v>1</v>
       </c>
-      <c r="Q11" t="s">
-        <v>23</v>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="A12" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1">
-        <v>1</v>
-      </c>
-      <c r="H12" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J12" s="1" t="s">
+      <c r="B12" t="s">
         <v>69</v>
       </c>
-      <c r="K12" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N12" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O12" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P12" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>55</v>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" t="s">
+        <v>71</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="b">
+        <v>1</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
       </c>
       <c r="R12" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="A13" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="B13" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="1">
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>0.97793468667255079</v>
       </c>
-      <c r="H13" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K13" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N13" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O13" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P13" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>55</v>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
       </c>
       <c r="R13" t="s">
-        <v>92</v>
-      </c>
-      <c r="S13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0.2166301969365427</v>
+      </c>
+      <c r="H14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="K14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S14" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F14" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0.5110896817743491</v>
-      </c>
-      <c r="H14" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K14" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M14" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N14" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O14" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P14" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S14" t="s">
+    <row r="15" spans="1:19" s="1" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0.97662337662337662</v>
+      </c>
+      <c r="H15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="K16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S16" s="1" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>81</v>
-      </c>
-      <c r="F15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I15" t="s">
-        <v>82</v>
-      </c>
-      <c r="J15" t="s">
-        <v>83</v>
-      </c>
-      <c r="K15" t="b">
-        <v>1</v>
-      </c>
-      <c r="L15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N15" t="b">
-        <v>1</v>
-      </c>
-      <c r="O15" t="b">
-        <v>1</v>
-      </c>
-      <c r="P15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F16" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="K16" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M16" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N16" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="O16" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="P16" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="R16" s="1"/>
-      <c r="S16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B25" t="s">
-        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S16" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
